--- a/data/trans_dic/POLIPATOLOGIA_Lim_2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_2-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,35; 21,07</t>
+          <t>15,46; 21,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,3; 17,88</t>
+          <t>12,63; 18,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,45; 27,2</t>
+          <t>20,21; 27,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,38; 36,61</t>
+          <t>29,68; 36,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,77; 31,86</t>
+          <t>24,92; 31,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,62; 34,62</t>
+          <t>25,2; 34,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,09; 28,07</t>
+          <t>23,27; 28,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,39; 23,89</t>
+          <t>19,38; 23,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,93; 29,97</t>
+          <t>24,54; 30,07</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,96</t>
+          <t>14,89; 19,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 17,37</t>
+          <t>12,77; 17,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,76; 16,73</t>
+          <t>5,78; 16,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,36; 33,11</t>
+          <t>27,09; 32,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,05; 28,96</t>
+          <t>23,07; 28,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,23; 33,98</t>
+          <t>28,94; 33,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,81; 25,87</t>
+          <t>21,74; 25,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,7; 22,63</t>
+          <t>18,84; 22,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,94; 23,99</t>
+          <t>13,92; 24,18</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,07; 17,5</t>
+          <t>12,04; 17,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,5; 16,26</t>
+          <t>11,55; 16,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 20,65</t>
+          <t>14,71; 20,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,05; 28,92</t>
+          <t>22,41; 28,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,11; 26,41</t>
+          <t>20,41; 26,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,7; 32,21</t>
+          <t>11,75; 32,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,1; 22,52</t>
+          <t>18,19; 22,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,6; 20,65</t>
+          <t>16,58; 20,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,89; 24,87</t>
+          <t>14,33; 25,01</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,32; 20,66</t>
+          <t>15,22; 20,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,26; 18,03</t>
+          <t>13,34; 18,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,58; 21,62</t>
+          <t>16,66; 21,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,66; 31,62</t>
+          <t>25,68; 31,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,93; 28,85</t>
+          <t>22,95; 28,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,34; 35,04</t>
+          <t>25,86; 35,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,48; 25,45</t>
+          <t>21,53; 25,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,17; 23,05</t>
+          <t>19,15; 23,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,76; 27,91</t>
+          <t>23,13; 28,01</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,73; 18,34</t>
+          <t>15,72; 18,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,72; 16,16</t>
+          <t>13,68; 16,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,6; 18,98</t>
+          <t>13,23; 19,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,69; 30,8</t>
+          <t>27,84; 30,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,22; 27,3</t>
+          <t>24,29; 27,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,13; 32,18</t>
+          <t>23,51; 32,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,16; 24,31</t>
+          <t>22,25; 24,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,41; 21,46</t>
+          <t>19,38; 21,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,31; 25,31</t>
+          <t>20,14; 25,29</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>108017; 148252</t>
+          <t>108736; 152039</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>82985; 120632</t>
+          <t>85207; 121846</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>129941; 172813</t>
+          <t>128395; 172143</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>204823; 255223</t>
+          <t>206858; 256465</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>166649; 214384</t>
+          <t>167660; 214004</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>178611; 251120</t>
+          <t>182801; 252458</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>323356; 393140</t>
+          <t>325833; 392772</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>261354; 321902</t>
+          <t>261216; 323033</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>325607; 407840</t>
+          <t>333884; 409154</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>151333; 203224</t>
+          <t>151594; 200868</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>132184; 177568</t>
+          <t>130610; 175570</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80599; 199601</t>
+          <t>68977; 196898</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>282389; 341757</t>
+          <t>279617; 340335</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>240414; 302054</t>
+          <t>240631; 301966</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>280232; 325733</t>
+          <t>277427; 324138</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>447216; 530387</t>
+          <t>445783; 526171</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>386280; 467479</t>
+          <t>389068; 465250</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>299879; 516190</t>
+          <t>299564; 520159</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91442; 132552</t>
+          <t>91230; 133992</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87321; 123512</t>
+          <t>87705; 124125</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101081; 145537</t>
+          <t>103669; 146131</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>171362; 224731</t>
+          <t>174180; 223471</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>157878; 207326</t>
+          <t>160184; 205434</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>127917; 300621</t>
+          <t>109634; 300995</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>277765; 345671</t>
+          <t>279215; 343222</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>256411; 318885</t>
+          <t>256131; 316322</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>227577; 407374</t>
+          <t>234666; 409687</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>145149; 195842</t>
+          <t>144221; 193174</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>124338; 169081</t>
+          <t>125115; 170219</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>153659; 200358</t>
+          <t>154453; 196350</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>269909; 332634</t>
+          <t>270174; 332070</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>239339; 301136</t>
+          <t>239501; 299518</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>277434; 383675</t>
+          <t>283200; 385433</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>429586; 508916</t>
+          <t>430553; 509160</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>379909; 456674</t>
+          <t>379464; 456355</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>460117; 564357</t>
+          <t>467695; 566209</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>539147; 628616</t>
+          <t>538765; 628083</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>465684; 548403</t>
+          <t>464515; 548687</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>470623; 656562</t>
+          <t>457566; 659443</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>985463; 1095935</t>
+          <t>990630; 1099426</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>858554; 967781</t>
+          <t>860858; 968200</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>895754; 1194646</t>
+          <t>872848; 1194874</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1547932; 1698386</t>
+          <t>1554153; 1693328</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1346697; 1488780</t>
+          <t>1344647; 1484176</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1456828; 1814962</t>
+          <t>1444766; 1814112</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_Lim_2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_2-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,46; 21,61</t>
+          <t>14,99; 21,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,63; 18,06</t>
+          <t>12,48; 18,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,21; 27,09</t>
+          <t>19,99; 26,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,68; 36,79</t>
+          <t>29,21; 36,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,92; 31,81</t>
+          <t>24,15; 31,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,2; 34,81</t>
+          <t>30,3; 35,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,27; 28,04</t>
+          <t>23,23; 27,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,38; 23,97</t>
+          <t>19,47; 23,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,54; 30,07</t>
+          <t>25,93; 30,17</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,89; 19,73</t>
+          <t>14,87; 19,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,77; 17,17</t>
+          <t>13,06; 17,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 16,51</t>
+          <t>13,42; 17,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,09; 32,97</t>
+          <t>27,06; 33,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,07; 28,95</t>
+          <t>23,37; 29,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,94; 33,81</t>
+          <t>29,02; 33,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,74; 25,67</t>
+          <t>21,94; 25,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,84; 22,53</t>
+          <t>18,71; 22,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,92; 24,18</t>
+          <t>21,67; 25,21</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,04; 17,69</t>
+          <t>11,91; 17,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,55; 16,34</t>
+          <t>11,26; 16,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,71; 20,74</t>
+          <t>14,33; 19,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,41; 28,75</t>
+          <t>22,38; 29,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,41; 26,17</t>
+          <t>20,21; 26,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,75; 32,25</t>
+          <t>28,73; 34,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 22,36</t>
+          <t>18,07; 22,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,58; 20,48</t>
+          <t>16,39; 20,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,33; 25,01</t>
+          <t>22,21; 26,36</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,22; 20,38</t>
+          <t>15,15; 20,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,34; 18,16</t>
+          <t>13,44; 18,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,66; 21,19</t>
+          <t>16,32; 21,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,68; 31,57</t>
+          <t>25,66; 31,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,95; 28,7</t>
+          <t>23,0; 29,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,86; 35,2</t>
+          <t>31,33; 36,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,53; 25,46</t>
+          <t>21,56; 25,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,15; 23,03</t>
+          <t>19,05; 22,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,13; 28,01</t>
+          <t>24,76; 28,25</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,72; 18,33</t>
+          <t>15,65; 18,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,68; 16,16</t>
+          <t>13,71; 16,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,23; 19,06</t>
+          <t>16,91; 19,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,84; 30,9</t>
+          <t>27,74; 30,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,29; 27,32</t>
+          <t>24,22; 27,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,51; 32,19</t>
+          <t>31,23; 33,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,25; 24,24</t>
+          <t>22,12; 24,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,38; 21,39</t>
+          <t>19,49; 21,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,14; 25,29</t>
+          <t>24,43; 26,52</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>149331</t>
+          <t>159524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>225472</t>
+          <t>240778</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>374803</t>
+          <t>400302</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>108736; 152039</t>
+          <t>105424; 147805</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85207; 121846</t>
+          <t>84232; 121800</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128395; 172143</t>
+          <t>138093; 182625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>206858; 256465</t>
+          <t>203607; 254082</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>167660; 214004</t>
+          <t>162502; 213846</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>182801; 252458</t>
+          <t>222482; 262057</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>325833; 392772</t>
+          <t>325291; 389760</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>261216; 323033</t>
+          <t>262368; 321726</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>333884; 409154</t>
+          <t>369515; 429907</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148691</t>
+          <t>162627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>301166</t>
+          <t>334189</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>449858</t>
+          <t>496817</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>151594; 200868</t>
+          <t>151376; 201212</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>130610; 175570</t>
+          <t>133541; 179792</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68977; 196898</t>
+          <t>140783; 187198</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>279617; 340335</t>
+          <t>279356; 340623</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>240631; 301966</t>
+          <t>243748; 304068</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>277427; 324138</t>
+          <t>310989; 361197</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>445783; 526171</t>
+          <t>449758; 527320</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>389068; 465250</t>
+          <t>386347; 463631</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>299564; 520159</t>
+          <t>459439; 534603</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121352</t>
+          <t>134894</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>224042</t>
+          <t>257718</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>345394</t>
+          <t>392612</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91230; 133992</t>
+          <t>90233; 132760</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87705; 124125</t>
+          <t>85512; 123337</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103669; 146131</t>
+          <t>115104; 159939</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>174180; 223471</t>
+          <t>173969; 226436</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>160184; 205434</t>
+          <t>158614; 206393</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>109634; 300995</t>
+          <t>233358; 280389</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>279215; 343222</t>
+          <t>277288; 345181</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>256131; 316322</t>
+          <t>253082; 318356</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>234666; 409687</t>
+          <t>358795; 425856</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175720</t>
+          <t>183947</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>348923</t>
+          <t>376729</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>524643</t>
+          <t>560677</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>144221; 193174</t>
+          <t>143567; 195345</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>125115; 170219</t>
+          <t>125990; 169149</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>154453; 196350</t>
+          <t>161529; 209418</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>270174; 332070</t>
+          <t>269950; 329378</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>239501; 299518</t>
+          <t>240047; 303187</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>283200; 385433</t>
+          <t>350640; 404187</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>430553; 509160</t>
+          <t>431117; 512165</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>379464; 456355</t>
+          <t>377450; 453430</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>467695; 566209</t>
+          <t>522196; 595922</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>595095</t>
+          <t>640992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1099603</t>
+          <t>1209415</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1694698</t>
+          <t>1850407</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>538765; 628083</t>
+          <t>536420; 633209</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>464515; 548687</t>
+          <t>465378; 550763</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>457566; 659443</t>
+          <t>597395; 691624</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>990630; 1099426</t>
+          <t>987012; 1089080</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>860858; 968200</t>
+          <t>858479; 975038</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>872848; 1194874</t>
+          <t>1167141; 1265328</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1554153; 1693328</t>
+          <t>1545276; 1696504</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1344647; 1484176</t>
+          <t>1352608; 1490115</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1444766; 1814112</t>
+          <t>1775947; 1927855</t>
         </is>
       </c>
     </row>
